--- a/data/Fichier final (RT+sol)_with_smiles_Unique_CAS.xlsx
+++ b/data/Fichier final (RT+sol)_with_smiles_Unique_CAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1662,19 +1662,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1-BROMO-3-METHYLBUTANE</t>
+          <t>1-Benzofuran-5-carboxylic_acid</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>107-82-4</t>
+          <t>90721-27-0</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>4.429</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1682,23 +1682,23 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>CC(C)CCBr</t>
+          <t>C1=CC2=C(C=CO2)C=C1C(=O)O</t>
         </is>
       </c>
     </row>
@@ -1715,16 +1715,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1-Benzofuran-5-carboxylic_acid</t>
+          <t>1-Bromo-4-(trifluoromethoxy)benzene</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>90721-27-0</t>
+          <t>407-14-7</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.429</v>
+        <v>5.937</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1735,23 +1735,23 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>C1=CC2=C(C=CO2)C=C1C(=O)O</t>
+          <t>C1=CC(=CC=C1OC(F)(F)F)Br</t>
         </is>
       </c>
     </row>
@@ -1768,19 +1768,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1-Benzylpiperidine</t>
+          <t>1-Bromopentanemethylbenzene</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2905-56-8</t>
+          <t>5153-40-2</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>6.696</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>C1CCN(CC1)CC2=CC=CC=C2</t>
+          <t>CC1=C(C(=C(C(=C1C)C)Br)C)C</t>
         </is>
       </c>
     </row>
@@ -1821,16 +1821,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1-Bromo-4-(trifluoromethoxy)benzene</t>
+          <t>1-Phenyl-5-(trifluoromethyl)-1H-pyrazole-4-carboxylic_acid</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>407-14-7</t>
+          <t>98534-81-7</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5.937</v>
+        <v>4.911</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1OC(F)(F)F)Br</t>
+          <t>C1=CC=C(C=C1)N2C(=C(C=N2)C(=O)O)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -1874,16 +1874,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1-Bromopentanemethylbenzene</t>
+          <t>1-Pyrenemethanol</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5153-40-2</t>
+          <t>24463-15-8</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6.696</v>
+        <v>5.4</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CC1=C(C(=C(C(=C1C)C)Br)C)C</t>
+          <t>C1=CC2=C3C(=C1)C=CC4=C(C=CC(=C43)C=C2)CO</t>
         </is>
       </c>
     </row>
@@ -1927,16 +1927,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1-Phenyl-5-(trifluoromethyl)-1H-pyrazole-4-carboxylic_acid</t>
+          <t>1-Tosyl-2,5-dihydro-1H-pyrrole</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>98534-81-7</t>
+          <t>16851-72-2</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.911</v>
+        <v>5.089</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)N2C(=C(C=N2)C(=O)O)C(F)(F)F</t>
+          <t>CC1=CC=C(C=C1)S(=O)(=O)N2CC=CC2</t>
         </is>
       </c>
     </row>
@@ -1980,16 +1980,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1-Pyrenemethanol</t>
+          <t>2,2",4,4"-Tetramethylbenzophenone</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24463-15-8</t>
+          <t>3478-88-4</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.4</v>
+        <v>6.309</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>C1=CC2=C3C(=C1)C=CC4=C(C=CC(=C43)C=C2)CO</t>
+          <t>CC1=CC(=C(C=C1)C(=O)C2=C(C=C(C=C2)C)C)C</t>
         </is>
       </c>
     </row>
@@ -2033,16 +2033,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1-Tosyl-2,5-dihydro-1H-pyrrole</t>
+          <t>2,2,2-TRIFLUOROACETOPHENONE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16851-72-2</t>
+          <t>434-45-7</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.089</v>
+        <v>4.383</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -2062,14 +2062,14 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>CC1=CC=C(C=C1)S(=O)(=O)N2CC=CC2</t>
+          <t>C1=CC=C(C=C1)C(=O)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -2086,16 +2086,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2,2",4,4"-Tetramethylbenzophenone</t>
+          <t>2,3,4-Trifluorobenzoic acid</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3478-88-4</t>
+          <t>61079-72-9</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6.309</v>
+        <v>4.672</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>CC1=CC(=C(C=C1)C(=O)C2=C(C=C(C=C2)C)C)C</t>
+          <t>C1=CC(=C(C(=C1C(=O)O)F)F)F</t>
         </is>
       </c>
     </row>
@@ -2139,16 +2139,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2,2,2-TRIFLUOROACETOPHENONE</t>
+          <t>2,3,6,7,10,11-Hexamethoxytriphenylene</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>434-45-7</t>
+          <t>808-57-1</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.383</v>
+        <v>5.531</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -2159,23 +2159,23 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)C(=O)C(F)(F)F</t>
+          <t>COC1=C(C=C2C(=C1)C3=CC(=C(C=C3C4=CC(=C(C=C24)OC)OC)OC)OC)OC</t>
         </is>
       </c>
     </row>
@@ -2192,16 +2192,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2,3,4-Trifluorobenzoic acid</t>
+          <t>2,4,6-Tris(bromomethyl)mesitylene</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>61079-72-9</t>
+          <t>21988-87-4</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.672</v>
+        <v>6.232</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -2212,23 +2212,23 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C(=C1C(=O)O)F)F)F</t>
+          <t>CC1=C(C(=C(C(=C1CBr)C)CBr)C)CBr</t>
         </is>
       </c>
     </row>
@@ -2245,16 +2245,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2,3,6,7,10,11-Hexamethoxytriphenylene</t>
+          <t>2,4-Dichlorophenol</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>808-57-1</t>
+          <t>120-83-2</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.531</v>
+        <v>4.997</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -2265,23 +2265,23 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>COC1=C(C=C2C(=C1)C3=CC(=C(C=C3C4=CC(=C(C=C24)OC)OC)OC)OC)OC</t>
+          <t>C1=CC(=C(C=C1Cl)Cl)O</t>
         </is>
       </c>
     </row>
@@ -2298,16 +2298,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2,4,6-Tris(bromomethyl)mesitylene</t>
+          <t>2,6-Bis[(4S)-4-phenyl-2-oxazolinyl]pyridine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21988-87-4</t>
+          <t>174500-20-0</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6.232</v>
+        <v>5.362</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -2330,11 +2330,11 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>CC1=C(C(=C(C(=C1CBr)C)CBr)C)CBr</t>
+          <t>C1[C@@H](N=C(O1)C2=NC(=CC=C2)C3=N[C@H](CO3)C4=CC=CC=C4)C5=CC=CC=C5</t>
         </is>
       </c>
     </row>
@@ -2351,16 +2351,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2,4-Dichlorophenol</t>
+          <t>2,6-Dichloroiodobenzene</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>120-83-2</t>
+          <t>19230-28-5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.997</v>
+        <v>6.045</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C=C1Cl)Cl)O</t>
+          <t>C1=CC(=C(C(=C1)Cl)I)Cl</t>
         </is>
       </c>
     </row>
@@ -2404,16 +2404,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2,6-Bis[(4S)-4-phenyl-2-oxazolinyl]pyridine</t>
+          <t>2,6-Diisopropylphenol</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>174500-20-0</t>
+          <t>2078-54-8</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5.362</v>
+        <v>5.797</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>C1[C@@H](N=C(O1)C2=NC(=CC=C2)C3=N[C@H](CO3)C4=CC=CC=C4)C5=CC=CC=C5</t>
+          <t>CC(C)C1=C(C(=CC=C1)C(C)C)O</t>
         </is>
       </c>
     </row>
@@ -2457,16 +2457,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2,6-Dichloroiodobenzene</t>
+          <t>2,6-Dimethoxy-1,4-benzoquinone</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19230-28-5</t>
+          <t>530-55-2</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6.045</v>
+        <v>3.493</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C(=C1)Cl)I)Cl</t>
+          <t>COC1=CC(=O)C=C(C1=O)OC</t>
         </is>
       </c>
     </row>
@@ -2510,16 +2510,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2,6-Diisopropylphenol</t>
+          <t>2,6-Dimethoxybenzoyl_chloride</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2078-54-8</t>
+          <t>1989-53-3</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.797</v>
+        <v>3.843</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>CC(C)C1=C(C(=CC=C1)C(C)C)O</t>
+          <t>COC1=C(C(=CC=C1)OC)C(=O)Cl</t>
         </is>
       </c>
     </row>
@@ -2563,16 +2563,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2,6-Dimethoxy-1,4-benzoquinone</t>
+          <t>2-(3-Chlorophenoxy)propionic-acid</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>530-55-2</t>
+          <t>101-10-0</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3.493</v>
+        <v>4.927</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>COC1=CC(=O)C=C(C1=O)OC</t>
+          <t>CC(C(=O)O)OC1=CC(=CC=C1)Cl</t>
         </is>
       </c>
     </row>
@@ -2616,16 +2616,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2,6-Dimethoxybenzoyl_chloride</t>
+          <t>2-(4-Chlorobenzoyl)benzoic_acid</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1989-53-3</t>
+          <t>85-56-3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.843</v>
+        <v>5.135</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>COC1=C(C(=CC=C1)OC)C(=O)Cl</t>
+          <t>C1=CC=C(C(=C1)C(=O)C2=CC=C(C=C2)Cl)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -2669,16 +2669,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2-(3-Chlorophenoxy)propionic-acid</t>
+          <t>2-(Diphenylphosphino)benzoic-acid</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>101-10-0</t>
+          <t>17261-28-8</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4.927</v>
+        <v>5.731</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CC(C(=O)O)OC1=CC(=CC=C1)Cl</t>
+          <t>C1=CC=C(C=C1)P(C2=CC=CC=C2)C3=CC=CC=C3C(=O)O</t>
         </is>
       </c>
     </row>
@@ -2722,16 +2722,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2-(4-Chlorobenzoyl)benzoic_acid</t>
+          <t>2-(Trifluoromethyl)pyridine-4-carboxylic_acid</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>85-56-3</t>
+          <t>131747-41-6</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5.135</v>
+        <v>4.521</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -2745,20 +2745,20 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>C1=CC=C(C(=C1)C(=O)C2=CC=C(C=C2)Cl)C(=O)O</t>
+          <t>C1=CN=C(C=C1C(=O)O)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -2775,16 +2775,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2-(Diphenylphosphino)benzoic-acid</t>
+          <t>2-Amino-4-phenylphenol</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17261-28-8</t>
+          <t>1134-36-7</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5.731</v>
+        <v>4.231</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -2804,14 +2804,14 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)P(C2=CC=CC=C2)C3=CC=CC=C3C(=O)O</t>
+          <t>C1=CC=C(C=C1)C2=CC(=C(C=C2)O)N</t>
         </is>
       </c>
     </row>
@@ -2828,16 +2828,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2-(Trifluoromethyl)pyridine-4-carboxylic_acid</t>
+          <t>2-Amino-6-bromopyridine</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>131747-41-6</t>
+          <t>19798-81-3</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.521</v>
+        <v>4.028</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -2857,14 +2857,14 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>C1=CN=C(C=C1C(=O)O)C(F)(F)F</t>
+          <t>C1=CC(=NC(=C1)Br)N</t>
         </is>
       </c>
     </row>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2-Amino-4-phenylphenol</t>
+          <t xml:space="preserve">2-Benzyloxybenzoic_acid </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1134-36-7</t>
+          <t>14389-86-7</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.231</v>
+        <v>5.023</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -2901,23 +2901,23 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)C2=CC(=C(C=C2)O)N</t>
+          <t>C1=CC=C(C=C1)COC2=CC=CC=C2C(=O)O</t>
         </is>
       </c>
     </row>
@@ -2934,16 +2934,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2-Amino-6-bromopyridine</t>
+          <t>2-Bromo-2',6'-diisopropoxy-1,1'-biphenyl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19798-81-3</t>
+          <t>870703-70-1</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.028</v>
+        <v>6.433</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>C1=CC(=NC(=C1)Br)N</t>
+          <t>CC(C)OC1=C(C(=CC=C1)OC(C)C)C2=CC=CC=C2Br</t>
         </is>
       </c>
     </row>
@@ -2987,16 +2987,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-Benzyloxybenzoic_acid </t>
+          <t>2-Bromo-5-(trifluoromethyl)benzaldehyde</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14389-86-7</t>
+          <t>102684-91-3</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.023</v>
+        <v>5.538</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)COC2=CC=CC=C2C(=O)O</t>
+          <t>C1=CC(=C(C=C1C(F)(F)F)C=O)Br</t>
         </is>
       </c>
     </row>
@@ -3040,16 +3040,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2-Bromo-2',6'-diisopropoxy-1,1'-biphenyl</t>
+          <t>2-Bromo-5-chlorotoluene</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>870703-70-1</t>
+          <t>14495-51-3</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.433</v>
+        <v>6.108</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>CC(C)OC1=C(C(=CC=C1)OC(C)C)C2=CC=CC=C2Br</t>
+          <t>CC1=C(C=CC(=C1)Cl)Br</t>
         </is>
       </c>
     </row>
@@ -3093,16 +3093,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2-Bromo-5-(trifluoromethyl)benzaldehyde</t>
+          <t>2-Bromoanthraquinone</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>102684-91-3</t>
+          <t>572-83-8</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.538</v>
+        <v>6.069</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C=C1C(F)(F)F)C=O)Br</t>
+          <t>C1=CC=C2C(=C1)C(=O)C3=C(C2=O)C=C(C=C3)Br</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2-Bromo-5-chlorotoluene</t>
+          <t>2-Bromonaphthalen-1-ol</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14495-51-3</t>
+          <t>771-15-3</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6.108</v>
+        <v>5.391</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>CC1=C(C=CC(=C1)Cl)Br</t>
+          <t>C1=CC=C2C(=C1)C=CC(=C2O)Br</t>
         </is>
       </c>
     </row>
@@ -3199,16 +3199,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2-Bromoanthraquinone</t>
+          <t>2-Bromophenethylamine</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>572-83-8</t>
+          <t>65185-58-2</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6.069</v>
+        <v>1.793</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>C1=CC=C2C(=C1)C(=O)C3=C(C2=O)C=C(C=C3)Br</t>
+          <t>C1=CC=C(C(=C1)CCN)Br</t>
         </is>
       </c>
     </row>
@@ -3252,16 +3252,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2-Bromonaphthalen-1-ol</t>
+          <t>2-Bromotoluene</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>771-15-3</t>
+          <t>95-46-5</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5.391</v>
+        <v>5.8</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>C1=CC=C2C(=C1)C=CC(=C2O)Br</t>
+          <t>CC1=CC=CC=C1Br</t>
         </is>
       </c>
     </row>
@@ -3305,16 +3305,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2-Bromophenethylamine</t>
+          <t>2-Hydroxy-4-(trifluoromethyl)aniline</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>65185-58-2</t>
+          <t>454-82-0</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.793</v>
+        <v>5.242</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -3325,23 +3325,23 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>C1=CC=C(C(=C1)CCN)Br</t>
+          <t>C1=CC(=C(C=C1C(F)(F)F)O)N</t>
         </is>
       </c>
     </row>
@@ -3358,16 +3358,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2-Bromotoluene</t>
+          <t>2-Iodobenzaldehyde</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>95-46-5</t>
+          <t>26260-02-6</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.8</v>
+        <v>5.212</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>CC1=CC=CC=C1Br</t>
+          <t>C1=CC=C(C(=C1)C=O)I</t>
         </is>
       </c>
     </row>
@@ -3411,16 +3411,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2-Hydroxy-4-(trifluoromethyl)aniline</t>
+          <t>2-Iodobenzyl_bromide</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>454-82-0</t>
+          <t>40400-13-3</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.242</v>
+        <v>5.787</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3440,14 +3440,14 @@
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C=C1C(F)(F)F)O)N</t>
+          <t>C1=CC=C(C(=C1)CBr)I</t>
         </is>
       </c>
     </row>
@@ -3464,16 +3464,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2-Iodobenzaldehyde</t>
+          <t>2-Iodopyridine</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26260-02-6</t>
+          <t>5029-67-4</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5.212</v>
+        <v>4.373</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>C1=CC=C(C(=C1)C=O)I</t>
+          <t>C1=CC=NC(=C1)I</t>
         </is>
       </c>
     </row>
@@ -3517,16 +3517,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2-Iodobenzyl_bromide</t>
+          <t>2-Isopropylthioxanthone</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>40400-13-3</t>
+          <t>5495-84-1</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5.787</v>
+        <v>6.361</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>C1=CC=C(C(=C1)CBr)I</t>
+          <t>CC(C)C1=CC2=C(C=C1)SC3=CC=CC=C3C2=O</t>
         </is>
       </c>
     </row>
@@ -3570,16 +3570,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2-Iodopyridine</t>
+          <t>2-Methyl-5-(trifluoromethyl)-1,3-benzoxazole</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5029-67-4</t>
+          <t>175785-41-8</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.373</v>
+        <v>5.205</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>C1=CC=NC(=C1)I</t>
+          <t>CC1=NC2=C(O1)C=CC(=C2)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -3623,16 +3623,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2-Isopropylthioxanthone</t>
+          <t>3,3-Dimethyl-1-indanone</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5495-84-1</t>
+          <t>26465-81-6</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6.361</v>
+        <v>5.04</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>CC(C)C1=CC2=C(C=C1)SC3=CC=CC=C3C2=O</t>
+          <t>CC1(CC(=O)C2=CC=CC=C21)C</t>
         </is>
       </c>
     </row>
@@ -3676,16 +3676,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2-Methyl-5-(trifluoromethyl)-1,3-benzoxazole</t>
+          <t>3,4,5-TRIBROMO-1H-PYRAZOLE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>175785-41-8</t>
+          <t>17635-44-8</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5.205</v>
+        <v>4.899</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -3705,14 +3705,14 @@
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>CC1=NC2=C(O1)C=CC(=C2)C(F)(F)F</t>
+          <t>C1(=C(NN=C1Br)Br)Br</t>
         </is>
       </c>
     </row>
@@ -3729,16 +3729,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3,3-Dimethyl-1-indanone</t>
+          <t>3,4,7,8-Tetramethyl-1,10-phenanthroline</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26465-81-6</t>
+          <t>1660-93-1</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.04</v>
+        <v>3.473</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>CC1(CC(=O)C2=CC=CC=C21)C</t>
+          <t>CC1=CN=C2C(=C1C)C=CC3=C(C(=CN=C32)C)C</t>
         </is>
       </c>
     </row>
@@ -3782,16 +3782,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3,4,5-TRIBROMO-1H-PYRAZOLE</t>
+          <t>3,5-Di-tert-butylbenzoic acid</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>17635-44-8</t>
+          <t>16225-26-6</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.899</v>
+        <v>5.809</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
@@ -3811,14 +3811,14 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>C1(=C(NN=C1Br)Br)Br</t>
+          <t>CC(C)(C)C1=CC(=CC(=C1)C(=O)O)C(C)(C)C</t>
         </is>
       </c>
     </row>
@@ -3835,16 +3835,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3,4,7,8-Tetramethyl-1,10-phenanthroline</t>
+          <t>3,5-Dibromotoluene</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1660-93-1</t>
+          <t>1611-92-3</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3.473</v>
+        <v>6.23</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -3855,23 +3855,23 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>CC1=CN=C2C(=C1C)C=CC3=C(C(=CN=C32)C)C</t>
+          <t>CC1=CC(=CC(=C1)Br)Br</t>
         </is>
       </c>
     </row>
@@ -3888,16 +3888,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3,5-Di-tert-butylbenzoic acid</t>
+          <t>3,5-Dimethylbenzoyl_chloride</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>16225-26-6</t>
+          <t>6613-44-1</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.809</v>
+        <v>4.754</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>CC(C)(C)C1=CC(=CC(=C1)C(=O)O)C(C)(C)C</t>
+          <t>CC1=CC(=CC(=C1)C(=O)Cl)C</t>
         </is>
       </c>
     </row>
@@ -3941,16 +3941,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3,5-Dibromotoluene</t>
+          <t>3,6-Dimethoxy-9H-carbazole</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1611-92-3</t>
+          <t>57103-01-2</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6.23</v>
+        <v>5.255</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -3970,14 +3970,14 @@
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>CC1=CC(=CC(=C1)Br)Br</t>
+          <t>COC1=CC2=C(C=C1)NC3=C2C=C(C=C3)OC</t>
         </is>
       </c>
     </row>
@@ -3994,16 +3994,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3,5-Dimethylbenzoyl_chloride</t>
+          <t>3-(2-Naphthyl)acrylic_acid</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6613-44-1</t>
+          <t>51557-26-7</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.754</v>
+        <v>5.054</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -4014,23 +4014,23 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>CC1=CC(=CC(=C1)C(=O)Cl)C</t>
+          <t>C1=CC=C2C=C(C=CC2=C1)/C=C/C(=O)O</t>
         </is>
       </c>
     </row>
@@ -4047,16 +4047,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3,6-Dimethoxy-9H-carbazole</t>
+          <t>3-(Phenylthio)propanoic-acid</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>57103-01-2</t>
+          <t>5219-65-8</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.255</v>
+        <v>4.682</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>COC1=CC2=C(C=C1)NC3=C2C=C(C=C3)OC</t>
+          <t>C1=CC=C(C=C1)SCCC(=O)O</t>
         </is>
       </c>
     </row>
@@ -4100,16 +4100,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3-(2-Naphthyl)acrylic_acid</t>
+          <t>3-(tert-Butoxycarbonyl)benzoic_acid</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>51557-26-7</t>
+          <t>33704-19-7</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5.054</v>
+        <v>5.126</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -4129,14 +4129,14 @@
         <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>C1=CC=C2C=C(C=CC2=C1)/C=C/C(=O)O</t>
+          <t>CC(C)(C)OC(=O)C1=CC=CC(=C1)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -4153,16 +4153,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3-(Phenylthio)propanoic-acid</t>
+          <t>3-Bromobenzoyl_chloride</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5219-65-8</t>
+          <t>1711-09-7</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.682</v>
+        <v>4.835</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)SCCC(=O)O</t>
+          <t>C1=CC(=CC(=C1)Br)C(=O)Cl</t>
         </is>
       </c>
     </row>
@@ -4206,16 +4206,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3-(tert-Butoxycarbonyl)benzoic_acid</t>
+          <t>3-Bromopropionyl_chloride</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>33704-19-7</t>
+          <t>15486-96-1</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5.126</v>
+        <v>2.918</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -4229,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)C1=CC=CC(=C1)C(=O)O</t>
+          <t>C(CBr)C(=O)Cl</t>
         </is>
       </c>
     </row>
@@ -4259,16 +4259,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3-Bromobenzoyl_chloride</t>
+          <t>3-Chloro-4-methoxyaniline</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1711-09-7</t>
+          <t>5345-54-0</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.835</v>
+        <v>3.019</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>C1=CC(=CC(=C1)Br)C(=O)Cl</t>
+          <t>COC1=C(C=C(C=C1)N)Cl</t>
         </is>
       </c>
     </row>
@@ -4312,16 +4312,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3-Bromopropionyl_chloride</t>
+          <t>3-[[(9H-Fluoren-9-ylmethoxy)carbonyl]amino]-2-naphthalenecarboxylic acid</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>15486-96-1</t>
+          <t>372159-75-6</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2.918</v>
+        <v>6.491</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -4332,23 +4332,23 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>C(CBr)C(=O)Cl</t>
+          <t>C1=CC=C2C=C(C(=CC2=C1)C(=O)O)NC(=O)OCC3C4=CC=CC=C4C5=CC=CC=C35</t>
         </is>
       </c>
     </row>
@@ -4365,16 +4365,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3-Chloro-4-methoxyaniline</t>
+          <t>4,4',4''-Trimethoxytrityl chloride</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5345-54-0</t>
+          <t>49757-42-8</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3.019</v>
+        <v>5.641</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -4388,10 +4388,10 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>COC1=C(C=C(C=C1)N)Cl</t>
+          <t>COC1=CC=C(C=C1)C(C2=CC=C(C=C2)OC)(C3=CC=C(C=C3)OC)Cl</t>
         </is>
       </c>
     </row>
@@ -4418,16 +4418,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3-[[(9H-Fluoren-9-ylmethoxy)carbonyl]amino]-2-naphthalenecarboxylic acid</t>
+          <t>4,4'-Dihydroxybiphenyl</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>372159-75-6</t>
+          <t>92-88-6</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6.491</v>
+        <v>4.374</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>C1=CC=C2C=C(C(=CC2=C1)C(=O)O)NC(=O)OCC3C4=CC=CC=C4C5=CC=CC=C35</t>
+          <t>C1=CC(=CC=C1C2=CC=C(C=C2)O)O</t>
         </is>
       </c>
     </row>
@@ -4471,16 +4471,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4,4',4''-Trimethoxytrityl chloride</t>
+          <t>4,4'-Dimethoxybenzophenone</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>49757-42-8</t>
+          <t>90-96-0</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5.641</v>
+        <v>5.396</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>COC1=CC=C(C=C1)C(C2=CC=C(C=C2)OC)(C3=CC=C(C=C3)OC)Cl</t>
+          <t>COC1=CC=C(C=C1)C(=O)C2=CC=C(C=C2)OC</t>
         </is>
       </c>
     </row>
@@ -4524,16 +4524,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>4,4'-Dihydroxybiphenyl</t>
+          <t>4,4?,4??-(1,3,5-TRIAZINE-2,4,6-TRIYL)TRIBENZALDEHYDE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>92-88-6</t>
+          <t>443922-06-3</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4.374</v>
+        <v>5.238</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1C2=CC=C(C=C2)O)O</t>
+          <t>C1=CC(=CC=C1C=O)C2=NC(=NC(=N2)C3=CC=C(C=C3)C=O)C4=CC=C(C=C4)C=O</t>
         </is>
       </c>
     </row>
@@ -4577,16 +4577,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4,4'-Dimethoxybenzophenone</t>
+          <t>4-(Bromomethyl)benzoic_acid</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>90-96-0</t>
+          <t>6232-88-8</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5.396</v>
+        <v>4.688</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -4603,17 +4603,17 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>COC1=CC=C(C=C1)C(=O)C2=CC=C(C=C2)OC</t>
+          <t>C1=CC(=CC=C1CBr)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -4630,16 +4630,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4,4?,4??-(1,3,5-TRIAZINE-2,4,6-TRIYL)TRIBENZALDEHYDE</t>
+          <t>4-(Hydroxymethyl)phenylacetic-acid</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>443922-06-3</t>
+          <t>73401-74-8</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5.238</v>
+        <v>3.398</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -4650,13 +4650,13 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1C=O)C2=NC(=NC(=N2)C3=CC=C(C=C3)C=O)C4=CC=C(C=C4)C=O</t>
+          <t>C1=CC(=CC=C1CC(=O)O)CO</t>
         </is>
       </c>
     </row>
@@ -4683,16 +4683,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>4-(Bromomethyl)benzoic_acid</t>
+          <t>4-(Trifluoroacetyl)phenacyl-bromide</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6232-88-8</t>
+          <t>1980063-91-9</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4.688</v>
+        <v>4.708</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1CBr)C(=O)O</t>
+          <t>C1=CC(=CC=C1C(=O)CBr)C(=O)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -4736,16 +4736,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4-(Hydroxymethyl)phenylacetic-acid</t>
+          <t>4-Bromo-3,5-dimethoxybenzoic acid</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>73401-74-8</t>
+          <t>56518-42-4</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.398</v>
+        <v>4.778</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1CC(=O)O)CO</t>
+          <t>COC1=CC(=CC(=C1Br)OC)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -4789,16 +4789,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>4-(Trifluoroacetyl)phenacyl-bromide</t>
+          <t>4-Bromo-L-phenylalanine</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1980063-91-9</t>
+          <t>24250-84-8</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.708</v>
+        <v>3.24</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1C(=O)CBr)C(=O)C(F)(F)F</t>
+          <t>C1=CC(=CC=C1C[C@@H](C(=O)O)N)Br</t>
         </is>
       </c>
     </row>
@@ -4842,19 +4842,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4-(Trifluoromethyl)benzylamine</t>
+          <t>4-Chlorobenzenesulfonic_acid</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3300-51-4</t>
+          <t>98-66-8</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>4.811</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1CN)C(F)(F)F</t>
+          <t>C1=CC(=CC=C1S(=O)(=O)O)Cl</t>
         </is>
       </c>
     </row>
@@ -4895,16 +4895,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4-Bromo-3,5-dimethoxybenzoic acid</t>
+          <t>4-Chloropyridine-3-carboxylic_acid</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>56518-42-4</t>
+          <t>10177-29-4</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.778</v>
+        <v>1.327</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>COC1=CC(=CC(=C1Br)OC)C(=O)O</t>
+          <t>C1=CN=CC(=C1Cl)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -4948,16 +4948,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4-Bromo-L-phenylalanine</t>
+          <t>4-Hydroxy-3,5-diiodobenzoic acid</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>24250-84-8</t>
+          <t>618-76-8</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3.24</v>
+        <v>4.728</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1C[C@@H](C(=O)O)N)Br</t>
+          <t>C1=C(C=C(C(=C1I)O)I)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -5001,16 +5001,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>4-Chlorobenzenesulfonic_acid</t>
+          <t>4-Hydroxyphthalic_acid</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>98-66-8</t>
+          <t>610-35-5</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.811</v>
+        <v>3.49</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -5024,20 +5024,20 @@
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>C1=CC(=CC=C1S(=O)(=O)O)Cl</t>
+          <t>C1=CC(=C(C=C1O)C(=O)O)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -5054,16 +5054,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>4-Chloropyridine-3-carboxylic_acid</t>
+          <t>4-Methoxybiphenyl</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10177-29-4</t>
+          <t>613-37-6</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.327</v>
+        <v>5.826</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -5077,20 +5077,20 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>C1=CN=CC(=C1Cl)C(=O)O</t>
+          <t>COC1=CC=C(C=C1)C2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5107,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>4-Hydroxy-3,5-diiodobenzoic acid</t>
+          <t>4-Methoxytriphenylamine</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>618-76-8</t>
+          <t>4316-51-2</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.728</v>
+        <v>6.436</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -5133,17 +5133,17 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>C1=C(C=C(C(=C1I)O)I)C(=O)O</t>
+          <t>COC1=CC=C(C=C1)N(C2=CC=CC=C2)C3=CC=CC=C3</t>
         </is>
       </c>
     </row>
@@ -5160,16 +5160,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4-Hydroxyphthalic_acid</t>
+          <t>4-tert-Butylbenzoyl_chloride</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>610-35-5</t>
+          <t>1710-98-1</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3.49</v>
+        <v>5.176</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -5183,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -5192,11 +5192,11 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C=C1O)C(=O)O)C(=O)O</t>
+          <t>CC(C)(C)C1=CC=C(C=C1)C(=O)Cl</t>
         </is>
       </c>
     </row>
@@ -5213,16 +5213,16 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>4-Methoxybiphenyl</t>
+          <t>5,7-Dimethyl-[1,2,4]triazolo[1,5-a]pyrimidine-2-carboxylic acid</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>613-37-6</t>
+          <t>87253-62-1</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5.826</v>
+        <v>3.115</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -5236,20 +5236,20 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>COC1=CC=C(C=C1)C2=CC=CC=C2</t>
+          <t>CC1=CC(=NC2=NC(=NN12)C(=O)O)C</t>
         </is>
       </c>
     </row>
@@ -5266,16 +5266,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4-Methoxytriphenylamine</t>
+          <t>5-(Trifluoromethyl)indole</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4316-51-2</t>
+          <t>100846-24-0</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6.436</v>
+        <v>5.375</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>COC1=CC=C(C=C1)N(C2=CC=CC=C2)C3=CC=CC=C3</t>
+          <t>C1=CC2=C(C=CN2)C=C1C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -5319,16 +5319,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>4-tert-Butylbenzoyl_chloride</t>
+          <t>5-(Trifluoromethyl)pyridine-2-carboxaldehyde</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1710-98-1</t>
+          <t>31224-82-5</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5.176</v>
+        <v>3.629</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -5348,14 +5348,14 @@
         <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>1</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>CC(C)(C)C1=CC=C(C=C1)C(=O)Cl</t>
+          <t>C1=CC(=NC=C1C(F)(F)F)C=O</t>
         </is>
       </c>
     </row>
@@ -5372,16 +5372,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>5,7-Dimethyl-[1,2,4]triazolo[1,5-a]pyrimidine-2-carboxylic acid</t>
+          <t>5-Bromo-2-furoic_acid</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>87253-62-1</t>
+          <t>585-70-6</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3.115</v>
+        <v>4.122</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>CC1=CC(=NC2=NC(=NN12)C(=O)O)C</t>
+          <t>C1=C(OC(=C1)Br)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -5425,16 +5425,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>5-(Trifluoromethyl)indole</t>
+          <t>5-Bromo-2-phenylpyridine</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>100846-24-0</t>
+          <t>27012-25-5</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5.375</v>
+        <v>5.763</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -5451,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>C1=CC2=C(C=CN2)C=C1C(F)(F)F</t>
+          <t>C1=CC=C(C=C1)C2=NC=C(C=C2)Br</t>
         </is>
       </c>
     </row>
@@ -5478,16 +5478,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>5-(Trifluoromethyl)pyridine-2-carboxaldehyde</t>
+          <t>6,6'-Dibromo-1,1'-bi-2-naphthol</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>31224-82-5</t>
+          <t>13185-00-7</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3.629</v>
+        <v>6.045</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
@@ -5507,14 +5507,14 @@
         <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>C1=CC(=NC=C1C(F)(F)F)C=O</t>
+          <t>C1=CC2=C(C=CC(=C2C3=C(C=CC4=C3C=CC(=C4)Br)O)O)C=C1Br</t>
         </is>
       </c>
     </row>
@@ -5531,16 +5531,16 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>5-Bromo-2-furoic_acid</t>
+          <t>8-Isoquinolinecarboxaldehyde</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>585-70-6</t>
+          <t>787615-01-4</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.122</v>
+        <v>3.063</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -5554,20 +5554,20 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>C1=C(OC(=C1)Br)C(=O)O</t>
+          <t>C1=CC2=C(C=NC=C2)C(=C1)C=O</t>
         </is>
       </c>
     </row>
@@ -5584,16 +5584,16 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5-Bromo-2-phenylpyridine</t>
+          <t>Aniline-2-sulfonic_acid</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>27012-25-5</t>
+          <t>88-21-1</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5.763</v>
+        <v>3.11</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
@@ -5604,23 +5604,23 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)C2=NC=C(C=C2)Br</t>
+          <t>C1=CC=C(C(=C1)N)S(=O)(=O)O</t>
         </is>
       </c>
     </row>
@@ -5637,16 +5637,16 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6,6'-Dibromo-1,1'-bi-2-naphthol</t>
+          <t>Bis(diphenylphosphino)methane</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>13185-00-7</t>
+          <t>2071-20-7</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6.045</v>
+        <v>6.727</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
@@ -5660,20 +5660,20 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>C1=CC2=C(C=CC(=C2C3=C(C=CC4=C3C=CC(=C4)Br)O)O)C=C1Br</t>
+          <t>C1=CC=C(C=C1)P(CP(C2=CC=CC=C2)C3=CC=CC=C3)C4=CC=CC=C4</t>
         </is>
       </c>
     </row>
@@ -5690,16 +5690,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8-Isoquinolinecarboxaldehyde</t>
+          <t>DL-beta-Phenylalanine</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>787615-01-4</t>
+          <t>614-19-7</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3.063</v>
+        <v>1.093</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -5710,23 +5710,23 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>C1=CC2=C(C=NC=C2)C(=C1)C=O</t>
+          <t>C1=CC=C(C=C1)C(CC(=O)O)N</t>
         </is>
       </c>
     </row>
@@ -5743,19 +5743,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Allyl-alpha-D-glucopyranoside</t>
+          <t>Dibenzyl-malonate</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>7464-56-4</t>
+          <t>15014-25-2</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>5.638</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5766,20 +5766,20 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>C=CCO[C@@H]1[C@@H]([C@H]([C@@H]([C@H](O1)CO)O)O)O</t>
+          <t>C1=CC=C(C=C1)COC(=O)CC(=O)OCC2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -5796,16 +5796,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Aniline-2-sulfonic_acid</t>
+          <t>Dibromomaleic-acid</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>88-21-1</t>
+          <t>608-37-7</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3.11</v>
+        <v>4.937</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>C1=CC=C(C(=C1)N)S(=O)(=O)O</t>
+          <t>C(=C(\C(=O)O)/Br)(\C(=O)O)/Br</t>
         </is>
       </c>
     </row>
@@ -5849,16 +5849,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bis(diphenylphosphino)methane</t>
+          <t>Diethyl 4-Methoxyphenylphosphonate</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2071-20-7</t>
+          <t>3762-33-2</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6.727</v>
+        <v>4.596</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -5869,13 +5869,13 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)P(CP(C2=CC=CC=C2)C3=CC=CC=C3)C4=CC=CC=C4</t>
+          <t>CCOP(=O)(C1=CC=C(C=C1)OC)OCC</t>
         </is>
       </c>
     </row>
@@ -5902,16 +5902,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DL-beta-Phenylalanine</t>
+          <t>Diethyl_phenylmalonate</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>614-19-7</t>
+          <t>83-13-6</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.093</v>
+        <v>5.385</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
@@ -5922,23 +5922,23 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)C(CC(=O)O)N</t>
+          <t>CCOC(=O)C(C1=CC=CC=C1)C(=O)OCC</t>
         </is>
       </c>
     </row>
@@ -5955,19 +5955,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Di-tert-butylcyclopentadiene</t>
+          <t>Dimethyl 1,3-cyclohexadiene-1,4-dicarboxylate</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>120937-44-2</t>
+          <t>1659-95-6</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>5.028</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5975,13 +5975,13 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>CC(C)(C)C1C=CC(=C1)C(C)(C)C</t>
+          <t>COC(=O)C1=CC=C(CC1)C(=O)OC</t>
         </is>
       </c>
     </row>
@@ -6008,16 +6008,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dibenzyl-malonate</t>
+          <t>Dimethyl 2,2'-bipyridine-4,4'-dicarboxylate</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15014-25-2</t>
+          <t>71071-46-0</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.638</v>
+        <v>5.269</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
@@ -6028,23 +6028,23 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>1</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)COC(=O)CC(=O)OCC2=CC=CC=C2</t>
+          <t>COC(=O)C1=CC(=NC=C1)C2=NC=CC(=C2)C(=O)OC</t>
         </is>
       </c>
     </row>
@@ -6061,16 +6061,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dibromomaleic-acid</t>
+          <t>Ethyl 2-cyclohexanoneacetate</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>608-37-7</t>
+          <t>24731-17-7</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4.937</v>
+        <v>4.697</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
@@ -6090,14 +6090,14 @@
         <v>1</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>C(=C(\C(=O)O)/Br)(\C(=O)O)/Br</t>
+          <t>CCOC(=O)CC1CCCCC1=O</t>
         </is>
       </c>
     </row>
@@ -6114,16 +6114,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Diethyl 4-Methoxyphenylphosphonate</t>
+          <t>Ethyl 3-thiopheneacetate</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>3762-33-2</t>
+          <t>37784-63-7</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4.596</v>
+        <v>5.044</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>CCOP(=O)(C1=CC=C(C=C1)OC)OCC</t>
+          <t>CCOC(=O)CC1=CSC=C1</t>
         </is>
       </c>
     </row>
@@ -6167,19 +6167,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Diethyl_dibutylmalonate</t>
+          <t>Ethyl 4,4,4-trifluoroacetoacetate</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>596-75-8</t>
+          <t>372-31-6</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>3.849</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>CCCCC(CCCC)(C(=O)OCC)C(=O)OCC</t>
+          <t>CCOC(=O)CC(=O)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -6220,16 +6220,16 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Diethyl_phenylmalonate</t>
+          <t>Ethyl mesitylglyoxylate</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>83-13-6</t>
+          <t>5524-57-2</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5.385</v>
+        <v>5.691</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>CCOC(=O)C(C1=CC=CC=C1)C(=O)OCC</t>
+          <t>CCOC(=O)C(=O)C1=C(C=C(C=C1C)C)C</t>
         </is>
       </c>
     </row>
@@ -6273,16 +6273,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dimethyl 1,3-cyclohexadiene-1,4-dicarboxylate</t>
+          <t>Ethyl-3-oxohexanoate</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1659-95-6</t>
+          <t>3249-68-1</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5.028</v>
+        <v>4.619</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>COC(=O)C1=CC=C(CC1)C(=O)OC</t>
+          <t>CCCC(=O)CC(=O)OCC</t>
         </is>
       </c>
     </row>
@@ -6326,16 +6326,16 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dimethyl 2,2'-bipyridine-4,4'-dicarboxylate</t>
+          <t>Ethyl-4-bromocrotonate</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>71071-46-0</t>
+          <t>37746-78-4</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5.269</v>
+        <v>4.986</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -6346,23 +6346,23 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>COC(=O)C1=CC(=NC=C1)C2=NC=CC(=C2)C(=O)OC</t>
+          <t>CCOC(=O)/C=C/CBr</t>
         </is>
       </c>
     </row>
@@ -6379,19 +6379,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dimethyl-propargylmalonate</t>
+          <t>Ethyl-4-iodobenzoate</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>95124-07-5</t>
+          <t>51934-41-9</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>5.872</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>COC(=O)C(CC#C)C(=O)OC</t>
+          <t>CCOC(=O)C1=CC=C(C=C1)I</t>
         </is>
       </c>
     </row>
@@ -6432,16 +6432,16 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ethyl 2-cyclohexanoneacetate</t>
+          <t>FMOC-D-ORN(ALOC)-OH</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>24731-17-7</t>
+          <t>214750-74-0</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4.697</v>
+        <v>5.271</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -6455,20 +6455,20 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>CCOC(=O)CC1CCCCC1=O</t>
+          <t>C=CCOC(=O)NCCC[C@H](C(=O)O)NC(=O)OCC1C2=CC=CC=C2C3=CC=CC=C13</t>
         </is>
       </c>
     </row>
@@ -6485,16 +6485,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ethyl 3-thiopheneacetate</t>
+          <t>Flavanone</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>37784-63-7</t>
+          <t>487-26-3</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5.044</v>
+        <v>5.511</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>CCOC(=O)CC1=CSC=C1</t>
+          <t>C1C(OC2=CC=CC=C2C1=O)C3=CC=CC=C3</t>
         </is>
       </c>
     </row>
@@ -6538,16 +6538,16 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ethyl 4,4,4-trifluoroacetoacetate</t>
+          <t>Flufenamic-acid</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>372-31-6</t>
+          <t>530-78-9</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3.849</v>
+        <v>5.775</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
@@ -6567,14 +6567,14 @@
         <v>1</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>CCOC(=O)CC(=O)C(F)(F)F</t>
+          <t>C1=CC=C(C(=C1)C(=O)O)NC2=CC=CC(=C2)C(F)(F)F</t>
         </is>
       </c>
     </row>
@@ -6591,16 +6591,16 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ethyl mesitylglyoxylate</t>
+          <t>Hematein</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5524-57-2</t>
+          <t>475-25-2</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5.691</v>
+        <v>4.766</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -6611,23 +6611,23 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>CCOC(=O)C(=O)C1=C(C=C(C=C1C)C)C</t>
+          <t>C1C2=CC(=C(C=C2C3=C4C=CC(=O)C(=C4OCC31O)O)O)O</t>
         </is>
       </c>
     </row>
@@ -6644,16 +6644,16 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethyl-3-oxohexanoate</t>
+          <t>METHYL 2-PHTHALIMIDOACETATE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3249-68-1</t>
+          <t>23244-58-8</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4.619</v>
+        <v>4.552</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>CCCC(=O)CC(=O)OCC</t>
+          <t>COC(=O)CN1C(=O)C2=CC=CC=C2C1=O</t>
         </is>
       </c>
     </row>
@@ -6697,16 +6697,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ethyl-4-bromocrotonate</t>
+          <t>Methyl 6-oxo-1,6-dihydropyridine-2-carboxylate</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>37746-78-4</t>
+          <t>30062-34-1</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4.986</v>
+        <v>2.95</v>
       </c>
       <c r="F119" t="n">
         <v>1</v>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>CCOC(=O)/C=C/CBr</t>
+          <t>COC(=O)C1=CC=CC(=O)N1</t>
         </is>
       </c>
     </row>
@@ -6750,16 +6750,16 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ethyl-4-iodobenzoate</t>
+          <t>Methyl-2,6-dimethoxybenzoate</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>51934-41-9</t>
+          <t>2065-27-2</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5.872</v>
+        <v>4.678</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>CCOC(=O)C1=CC=C(C=C1)I</t>
+          <t>COC1=C(C(=CC=C1)OC)C(=O)OC</t>
         </is>
       </c>
     </row>
@@ -6803,16 +6803,16 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FMOC-D-ORN(ALOC)-OH</t>
+          <t>Methyl-3-bromo-4-iodobenzoate</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>214750-74-0</t>
+          <t>249647-24-3</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5.271</v>
+        <v>5.904</v>
       </c>
       <c r="F121" t="n">
         <v>1</v>
@@ -6823,23 +6823,23 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>C=CCOC(=O)NCCC[C@H](C(=O)O)NC(=O)OCC1C2=CC=CC=C2C3=CC=CC=C13</t>
+          <t>COC(=O)C1=CC(=C(C=C1)I)Br</t>
         </is>
       </c>
     </row>
@@ -6856,16 +6856,16 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Flavanone</t>
+          <t>Methyl-6-Oxo-1,6-dihydropyridazine-3-carboxylate</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>487-26-3</t>
+          <t>63001-30-9</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5.511</v>
+        <v>2.406</v>
       </c>
       <c r="F122" t="n">
         <v>1</v>
@@ -6879,20 +6879,20 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>C1C(OC2=CC=CC=C2C1=O)C3=CC=CC=C3</t>
+          <t>COC(=O)C1=NNC(=O)C=C1</t>
         </is>
       </c>
     </row>
@@ -6909,16 +6909,16 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Flufenamic-acid</t>
+          <t>Methyl-diethylphosphonoacetate</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>530-78-9</t>
+          <t>1067-74-9</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5.775</v>
+        <v>3.718</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -6938,14 +6938,14 @@
         <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
         <v>1</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>C1=CC=C(C(=C1)C(=O)O)NC2=CC=CC(=C2)C(F)(F)F</t>
+          <t>CCOP(=O)(CC(=O)OC)OCC</t>
         </is>
       </c>
     </row>
@@ -6962,16 +6962,16 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hematein</t>
+          <t>N(im)-Trityl-L-histidine</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>475-25-2</t>
+          <t>35146-32-8</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4.766</v>
+        <v>3.928</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>C1C2=CC(=C(C=C2C3=C4C=CC(=O)C(=C4OCC31O)O)O)O</t>
+          <t>C1=CC=C(C=C1)C(C2=CC=CC=C2)(C3=CC=CC=C3)N4C=C(N=C4)C[C@@H](C(=O)O)N</t>
         </is>
       </c>
     </row>
@@ -7015,16 +7015,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>METHYL 2-PHTHALIMIDOACETATE</t>
+          <t>N,N-Dimethyl-L-phenylalanine</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>23244-58-8</t>
+          <t>17469-89-5</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4.552</v>
+        <v>2.119</v>
       </c>
       <c r="F125" t="n">
         <v>1</v>
@@ -7038,20 +7038,20 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>COC(=O)CN1C(=O)C2=CC=CC=C2C1=O</t>
+          <t>CN(C)[C@@H](CC1=CC=CC=C1)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -7068,16 +7068,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Methyl 6-oxo-1,6-dihydropyridine-2-carboxylate</t>
+          <t>N-Acetyl-L-tryptophan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>30062-34-1</t>
+          <t>1218-34-4</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2.95</v>
+        <v>3.949</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -7091,20 +7091,20 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>COC(=O)C1=CC=CC(=O)N1</t>
+          <t>CC(=O)N[C@@H](CC1=CNC2=CC=CC=C21)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -7121,16 +7121,16 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Methyl-2,6-dimethoxybenzoate</t>
+          <t>N-Benzylidenebenzylamine</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2065-27-2</t>
+          <t>780-25-6</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4.678</v>
+        <v>4.377</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>COC1=C(C(=CC=C1)OC)C(=O)OC</t>
+          <t>C1=CC=C(C=C1)CN=CC2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -7174,16 +7174,16 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Methyl-3-bromo-4-iodobenzoate</t>
+          <t>N-Phthaloylglycine</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>249647-24-3</t>
+          <t>4702-13-0</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5.904</v>
+        <v>4.073</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -7194,23 +7194,23 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>COC(=O)C1=CC(=C(C=C1)I)Br</t>
+          <t>C1=CC=C2C(=C1)C(=O)N(C2=O)CC(=O)O</t>
         </is>
       </c>
     </row>
@@ -7227,16 +7227,16 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Methyl-6-Oxo-1,6-dihydropyridazine-3-carboxylate</t>
+          <t>N-[(1,1-Dimethylethoxy)carbonyl]-L-histidine methyl_ester</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>63001-30-9</t>
+          <t>2488-14-4</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2.406</v>
+        <v>1.875</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -7256,14 +7256,14 @@
         <v>1</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>COC(=O)C1=NNC(=O)C=C1</t>
+          <t>CC(C)(C)OC(=O)N[C@@H](CC1=CN=CN1)C(=O)OC</t>
         </is>
       </c>
     </row>
@@ -7280,16 +7280,16 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Methyl-diethylphosphonoacetate</t>
+          <t>N-[(Phenylmethoxy)carbonyl]-O-(phenylmethyl)-L-serine_</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1067-74-9</t>
+          <t>20806-43-3</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3.718</v>
+        <v>5.197</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>CCOP(=O)(CC(=O)OC)OCC</t>
+          <t>C1=CC=C(C=C1)COC[C@@H](C(=O)O)NC(=O)OCC2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -7333,16 +7333,16 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>N(im)-Trityl-L-histidine</t>
+          <t>N6-[(1,1-Dimethylethoxy)carbonyl]-N2-[(9H-fluoren-9-ylmethoxy)carbonyl]-2-methyl-D-lysine</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>35146-32-8</t>
+          <t>1315449-94-5</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3.928</v>
+        <v>5.699</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
@@ -7356,20 +7356,20 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)C(C2=CC=CC=C2)(C3=CC=CC=C3)N4C=C(N=C4)C[C@@H](C(=O)O)N</t>
+          <t>C[C@@](CCCCNC(=O)OC(C)(C)C)(C(=O)O)NC(=O)OCC1C2=CC=CC=C2C3=CC=CC=C13</t>
         </is>
       </c>
     </row>
@@ -7386,16 +7386,16 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>N,N-Dimethyl-L-phenylalanine</t>
+          <t>N6-[(1,1-Dimethylethoxy)carbonyl]-N2-[(phenylmethoxy)carbonyl]-L-lysine</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>17469-89-5</t>
+          <t>2389-60-8</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2.119</v>
+        <v>5.033</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -7406,23 +7406,23 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>CN(C)[C@@H](CC1=CC=CC=C1)C(=O)O</t>
+          <t>CC(C)(C)OC(=O)NCCCC[C@@H](C(=O)O)NC(=O)OCC1=CC=CC=C1</t>
         </is>
       </c>
     </row>
@@ -7439,16 +7439,16 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>N-Acetyl-L-tryptophan</t>
+          <t>Nalpha-[(9H-Fluoren-9-ylmethoxy)carbonyl]-L-threonine tert-Butyl-Ester</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1218-34-4</t>
+          <t>120791-76-6</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3.949</v>
+        <v>5.649</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
@@ -7462,20 +7462,20 @@
         <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>CC(=O)N[C@@H](CC1=CNC2=CC=CC=C21)C(=O)O</t>
+          <t>C[C@H]([C@@H](C(=O)OC(C)(C)C)NC(=O)OCC1C2=CC=CC=C2C3=CC=CC=C13)O</t>
         </is>
       </c>
     </row>
@@ -7492,16 +7492,16 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>N-Benzylidenebenzylamine</t>
+          <t>Phenyl-benzoate</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>780-25-6</t>
+          <t>93-99-2</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4.377</v>
+        <v>5.68</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)CN=CC2=CC=CC=C2</t>
+          <t>C1=CC=C(C=C1)C(=O)OC2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -7545,16 +7545,16 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>N-Phthaloylglycine</t>
+          <t>Pindolol</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4702-13-0</t>
+          <t>13523-86-9</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4.073</v>
+        <v>2.175</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -7565,23 +7565,23 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" t="n">
         <v>1</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>C1=CC=C2C(=C1)C(=O)N(C2=O)CC(=O)O</t>
+          <t>CC(C)NCC(COC1=CC=CC2=C1C=CN2)O</t>
         </is>
       </c>
     </row>
@@ -7598,16 +7598,16 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>N-[(1,1-Dimethylethoxy)carbonyl]-L-histidine methyl_ester</t>
+          <t>Protocatechuic_acid</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2488-14-4</t>
+          <t>99-50-3</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1.875</v>
+        <v>2.834</v>
       </c>
       <c r="F136" t="n">
         <v>1</v>
@@ -7621,20 +7621,20 @@
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>1</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)N[C@@H](CC1=CN=CN1)C(=O)OC</t>
+          <t>C1=CC(=C(C=C1C(=O)O)O)O</t>
         </is>
       </c>
     </row>
@@ -7651,16 +7651,16 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>N-[(Phenylmethoxy)carbonyl]-O-(phenylmethyl)-L-serine_</t>
+          <t>Suberic_acid_monomethyl_ester</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20806-43-3</t>
+          <t>3946-32-5</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5.197</v>
+        <v>4.292</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
@@ -7674,20 +7674,20 @@
         <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
         <v>1</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)COC[C@@H](C(=O)O)NC(=O)OCC2=CC=CC=C2</t>
+          <t>COC(=O)CCCCCCC(=O)O</t>
         </is>
       </c>
     </row>
@@ -7704,16 +7704,16 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>N6-[(1,1-Dimethylethoxy)carbonyl]-N2-[(9H-fluoren-9-ylmethoxy)carbonyl]-2-methyl-D-lysine</t>
+          <t>Z-D-Glu-OBzl</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1315449-94-5</t>
+          <t>65706-99-2</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5.699</v>
+        <v>5.091</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
         <v>1</v>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>C[C@@](CCCCNC(=O)OC(C)(C)C)(C(=O)O)NC(=O)OCC1C2=CC=CC=C2C3=CC=CC=C13</t>
+          <t>C1=CC=C(C=C1)COC(=O)[C@@H](CCC(=O)O)NC(=O)OCC2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -7757,16 +7757,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>N6-[(1,1-Dimethylethoxy)carbonyl]-N2-[(phenylmethoxy)carbonyl]-L-lysine</t>
+          <t>Z-D-Phg-OH</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2389-60-8</t>
+          <t>17609-52-8</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5.033</v>
+        <v>5.081</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
@@ -7780,7 +7780,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>1</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)NCCCC[C@@H](C(=O)O)NC(=O)OCC1=CC=CC=C1</t>
+          <t>C1=CC=C(C=C1)COC(=O)N[C@H](C2=CC=CC=C2)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -7810,16 +7810,16 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nalpha-[(9H-Fluoren-9-ylmethoxy)carbonyl]-L-threonine tert-Butyl-Ester</t>
+          <t>meso-1,2-Dibromo-1,2-diphenylethane</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>120791-76-6</t>
+          <t>13440-24-9</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5.649</v>
+        <v>5.994</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -7830,23 +7830,23 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
         <v>1</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>C[C@H]([C@@H](C(=O)OC(C)(C)C)NC(=O)OCC1C2=CC=CC=C2C3=CC=CC=C13)O</t>
+          <t>C1=CC=C(C=C1)C(C(C2=CC=CC=C2)Br)Br</t>
         </is>
       </c>
     </row>
@@ -7863,16 +7863,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Phenyl-benzoate</t>
+          <t>mono-tert-Butyl_succinate</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>93-99-2</t>
+          <t>15026-17-2</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5.68</v>
+        <v>4.186</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -7892,14 +7892,14 @@
         <v>1</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>C1=CC=C(C=C1)C(=O)OC2=CC=CC=C2</t>
+          <t>CC(C)(C)OC(=O)CCC(=O)O</t>
         </is>
       </c>
     </row>
@@ -7916,16 +7916,16 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pindolol</t>
+          <t>pentafluorobenzyl-bromide</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>13523-86-9</t>
+          <t>1765-40-8</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2.175</v>
+        <v>5.716</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -7936,13 +7936,13 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>1</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>CC(C)NCC(COC1=CC=CC2=C1C=CN2)O</t>
+          <t>C(C1=C(C(=C(C(=C1F)F)F)F)F)Br</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Protocatechuic_acid</t>
+          <t>trans-1,2-Bis(phenylsulfonyl)ethylene</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>99-50-3</t>
+          <t>963-16-6</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2.834</v>
+        <v>5.192</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -7989,13 +7989,13 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>C1=CC(=C(C=C1C(=O)O)O)O</t>
+          <t>C1=CC=C(C=C1)S(=O)(=O)/C=C/S(=O)(=O)C2=CC=CC=C2</t>
         </is>
       </c>
     </row>
@@ -8022,16 +8022,16 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Suberic_acid_monomethyl_ester</t>
+          <t>trans-4-(9-Fluorenylmethyloxycarbonylaminomethyl)-cyclohexanoic_acid</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>3946-32-5</t>
+          <t>188715-40-4</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4.292</v>
+        <v>5.311</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
@@ -8042,23 +8042,23 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>COC(=O)CCCCCCC(=O)O</t>
+          <t>C1CC(CCC1CNC(=O)OCC2C3=CC=CC=C3C4=CC=CC=C24)C(=O)O</t>
         </is>
       </c>
     </row>
@@ -8075,16 +8075,16 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Z-D-Glu-OBzl</t>
+          <t>trans-Aconitic-acid</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>65706-99-2</t>
+          <t>4023-65-8</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5.091</v>
+        <v>1.606</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -8095,392 +8095,21 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="inlineStr">
-        <is>
-          <t>C1=CC=C(C=C1)COC(=O)[C@@H](CCC(=O)O)NC(=O)OCC2=CC=CC=C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Z-D-Phg-OH</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>17609-52-8</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>5.081</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>1</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="n">
-        <v>1</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>C1=CC=C(C=C1)COC(=O)N[C@H](C2=CC=CC=C2)C(=O)O</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>meso-1,2-Dibromo-1,2-diphenylethane</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>13440-24-9</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>5.994</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" t="n">
-        <v>1</v>
-      </c>
-      <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>C1=CC=C(C=C1)C(C(C2=CC=CC=C2)Br)Br</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>mono-tert-Butyl_succinate</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>15026-17-2</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>4.186</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>1</v>
-      </c>
-      <c r="I148" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" t="n">
-        <v>1</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>CC(C)(C)OC(=O)CCC(=O)O</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>pentafluorobenzyl-bromide</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>1765-40-8</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>5.716</v>
-      </c>
-      <c r="F149" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>1</v>
-      </c>
-      <c r="I149" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" t="n">
-        <v>1</v>
-      </c>
-      <c r="K149" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>C(C1=C(C(=C(C(=C1F)F)F)F)F)Br</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>trans-1,2-Bis(phenylsulfonyl)ethylene</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>963-16-6</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>5.192</v>
-      </c>
-      <c r="F150" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>C1=CC=C(C=C1)S(=O)(=O)/C=C/S(=O)(=O)C2=CC=CC=C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>trans-4-(9-Fluorenylmethyloxycarbonylaminomethyl)-cyclohexanoic_acid</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>188715-40-4</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>5.311</v>
-      </c>
-      <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>C1CC(CCC1CNC(=O)OCC2C3=CC=CC=C3C4=CC=CC=C24)C(=O)O</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>BlueBird</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>method_1</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>trans-Aconitic-acid</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>4023-65-8</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>1.606</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>matrix ID BlueBird 1</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>1</v>
-      </c>
-      <c r="I152" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" t="n">
-        <v>1</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="inlineStr">
         <is>
           <t>C(/C(=C\C(=O)O)/C(=O)O)C(=O)O</t>
         </is>
